--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2023.xlsx
@@ -2149,7 +2149,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:33</t>
+    <t xml:space="preserve">2026-09-17 14:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_i_ingr_mean_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">San Gregorio</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11101</t>
@@ -133,9 +133,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11302</t>
   </si>
   <si>
@@ -265,7 +262,7 @@
     <t xml:space="preserve">Tiltil</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5103</t>
@@ -547,7 +544,7 @@
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16101</t>
@@ -610,9 +607,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">16103</t>
   </si>
   <si>
@@ -754,7 +748,7 @@
     <t xml:space="preserve">16206</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">5105</t>
@@ -1282,7 +1276,7 @@
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1101</t>
@@ -1525,7 +1519,7 @@
     <t xml:space="preserve">Macrozona Sur</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8108</t>
@@ -1552,7 +1546,7 @@
     <t xml:space="preserve">Puerto Montt</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9101</t>
@@ -1579,7 +1573,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14101</t>
@@ -1591,7 +1585,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">8304</t>
@@ -1819,7 +1813,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">8305</t>
@@ -2173,7 +2167,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:42</t>
+    <t xml:space="preserve">2026-10-05 18:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2993,7 +2987,7 @@
         <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -3022,10 +3016,10 @@
         <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -3054,10 +3048,10 @@
         <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3086,10 +3080,10 @@
         <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3118,10 +3112,10 @@
         <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3150,10 +3144,10 @@
         <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -3182,10 +3176,10 @@
         <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>13</v>
@@ -3214,10 +3208,10 @@
         <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
@@ -3246,10 +3240,10 @@
         <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>13</v>
@@ -3275,25 +3269,25 @@
         <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1111165.12</v>
+        <v>1111165.13</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3307,25 +3301,25 @@
         <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1074141.12</v>
+        <v>1074141.13</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3339,19 +3333,19 @@
         <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3371,25 +3365,25 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>949489.12</v>
+        <v>949489.13</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3403,19 +3397,19 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3435,19 +3429,19 @@
         <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3467,19 +3461,19 @@
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3499,19 +3493,19 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3531,19 +3525,19 @@
         <v>13</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3563,19 +3557,19 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3595,19 +3589,19 @@
         <v>13</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3627,19 +3621,19 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3659,19 +3653,19 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3691,19 +3685,19 @@
         <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3723,25 +3717,25 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>532966.62</v>
+        <v>532966.63</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3755,25 +3749,25 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>527991.12</v>
+        <v>527991.13</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3787,19 +3781,19 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3819,19 +3813,19 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3851,19 +3845,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3883,19 +3877,19 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3915,19 +3909,19 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3947,19 +3941,19 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3979,19 +3973,19 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -4011,19 +4005,19 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -4043,19 +4037,19 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4075,19 +4069,19 @@
         <v>5</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4107,25 +4101,25 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>462240.62</v>
+        <v>462240.63</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4139,19 +4133,19 @@
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4171,19 +4165,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4203,19 +4197,19 @@
         <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4235,19 +4229,19 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4267,19 +4261,19 @@
         <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4299,19 +4293,19 @@
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4331,19 +4325,19 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4363,19 +4357,19 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4395,25 +4389,25 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>426741.12</v>
+        <v>426741.13</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4427,19 +4421,19 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4459,19 +4453,19 @@
         <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4491,19 +4485,19 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4523,19 +4517,19 @@
         <v>13</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4555,19 +4549,19 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4587,19 +4581,19 @@
         <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4619,19 +4613,19 @@
         <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4651,19 +4645,19 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4683,19 +4677,19 @@
         <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4715,19 +4709,19 @@
         <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4747,19 +4741,19 @@
         <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4779,19 +4773,19 @@
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4811,19 +4805,19 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4843,19 +4837,19 @@
         <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4875,19 +4869,19 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4907,19 +4901,19 @@
         <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4939,19 +4933,19 @@
         <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4971,19 +4965,19 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="F75" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -5003,19 +4997,19 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -5035,19 +5029,19 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -5067,19 +5061,19 @@
         <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5099,19 +5093,19 @@
         <v>5</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5131,19 +5125,19 @@
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5163,19 +5157,19 @@
         <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5195,19 +5189,19 @@
         <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5227,25 +5221,25 @@
         <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="F83" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>367327.62</v>
+        <v>367327.63</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5259,19 +5253,19 @@
         <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5291,19 +5285,19 @@
         <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="F85" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5323,19 +5317,19 @@
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5355,19 +5349,19 @@
         <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="F87" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5387,19 +5381,19 @@
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="F88" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5419,19 +5413,19 @@
         <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F89" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5451,19 +5445,19 @@
         <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5483,19 +5477,19 @@
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5515,19 +5509,19 @@
         <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5547,19 +5541,19 @@
         <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5579,19 +5573,19 @@
         <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5611,19 +5605,19 @@
         <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5643,19 +5637,19 @@
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5675,19 +5669,19 @@
         <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5707,19 +5701,19 @@
         <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5739,19 +5733,19 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5771,19 +5765,19 @@
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5803,19 +5797,19 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5835,19 +5829,19 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5867,19 +5861,19 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5899,19 +5893,19 @@
         <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5931,19 +5925,19 @@
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5963,19 +5957,19 @@
         <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5995,19 +5989,19 @@
         <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -6027,19 +6021,19 @@
         <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -6059,19 +6053,19 @@
         <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6091,19 +6085,19 @@
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6123,19 +6117,19 @@
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6155,19 +6149,19 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6187,19 +6181,19 @@
         <v>6</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6219,19 +6213,19 @@
         <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6251,19 +6245,19 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6283,19 +6277,19 @@
         <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6315,19 +6309,19 @@
         <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6347,19 +6341,19 @@
         <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6379,19 +6373,19 @@
         <v>5</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6411,19 +6405,19 @@
         <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6443,19 +6437,19 @@
         <v>6</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6475,19 +6469,19 @@
         <v>16</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6507,19 +6501,19 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6539,19 +6533,19 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6571,19 +6565,19 @@
         <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6603,19 +6597,19 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6635,19 +6629,19 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6667,19 +6661,19 @@
         <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6699,19 +6693,19 @@
         <v>16</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6731,19 +6725,19 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6763,19 +6757,19 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6795,25 +6789,25 @@
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>293747.12</v>
+        <v>293747.13</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6827,19 +6821,19 @@
         <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6859,19 +6853,19 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6891,19 +6885,19 @@
         <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6923,19 +6917,19 @@
         <v>6</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6955,19 +6949,19 @@
         <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6987,19 +6981,19 @@
         <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -7019,19 +7013,19 @@
         <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -7051,19 +7045,19 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7083,19 +7077,19 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7115,19 +7109,19 @@
         <v>5</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7147,19 +7141,19 @@
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7179,19 +7173,19 @@
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7211,19 +7205,19 @@
         <v>6</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7243,19 +7237,19 @@
         <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7275,19 +7269,19 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7307,19 +7301,19 @@
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7339,19 +7333,19 @@
         <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7371,19 +7365,19 @@
         <v>13</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7403,19 +7397,19 @@
         <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7435,19 +7429,19 @@
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7467,19 +7461,19 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7499,19 +7493,19 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7531,19 +7525,19 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7563,19 +7557,19 @@
         <v>6</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7595,19 +7589,19 @@
         <v>16</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7627,19 +7621,19 @@
         <v>16</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7659,19 +7653,19 @@
         <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7691,19 +7685,19 @@
         <v>6</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7723,19 +7717,19 @@
         <v>7</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7755,19 +7749,19 @@
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7787,25 +7781,25 @@
         <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>253791.62</v>
+        <v>253791.63</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7819,19 +7813,19 @@
         <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7851,19 +7845,19 @@
         <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7883,19 +7877,19 @@
         <v>16</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7915,19 +7909,19 @@
         <v>16</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7947,19 +7941,19 @@
         <v>16</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7979,19 +7973,19 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -8011,19 +8005,19 @@
         <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -8043,19 +8037,19 @@
         <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8075,19 +8069,19 @@
         <v>16</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8107,19 +8101,19 @@
         <v>5</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8139,25 +8133,25 @@
         <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>228631.12</v>
+        <v>228631.13</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8171,19 +8165,19 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8203,19 +8197,19 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8235,19 +8229,19 @@
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8267,19 +8261,19 @@
         <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8299,19 +8293,19 @@
         <v>7</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8331,19 +8325,19 @@
         <v>7</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8363,19 +8357,19 @@
         <v>7</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8395,19 +8389,19 @@
         <v>5</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8427,19 +8421,19 @@
         <v>7</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8459,19 +8453,19 @@
         <v>6</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8491,19 +8485,19 @@
         <v>16</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8523,19 +8517,19 @@
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8555,19 +8549,19 @@
         <v>16</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8587,19 +8581,19 @@
         <v>16</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8619,19 +8613,19 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8651,19 +8645,19 @@
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8683,19 +8677,19 @@
         <v>16</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8715,19 +8709,19 @@
         <v>16</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8747,25 +8741,25 @@
         <v>6</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>163156.62</v>
+        <v>163156.63</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8779,19 +8773,19 @@
         <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="F194" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E194" s="2" t="s">
+      <c r="G194" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G194" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8811,19 +8805,19 @@
         <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8843,19 +8837,19 @@
         <v>2</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8875,19 +8869,19 @@
         <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8907,19 +8901,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="F198" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8939,19 +8933,19 @@
         <v>2</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8971,19 +8965,19 @@
         <v>3</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -9003,19 +8997,19 @@
         <v>1</v>
       </c>
       <c r="C201" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D201" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="F201" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -9035,19 +9029,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D202" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="F202" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9067,19 +9061,19 @@
         <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9099,19 +9093,19 @@
         <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9131,19 +9125,19 @@
         <v>3</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9163,19 +9157,19 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9195,19 +9189,19 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9227,19 +9221,19 @@
         <v>2</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9259,19 +9253,19 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9291,19 +9285,19 @@
         <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9323,19 +9317,19 @@
         <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9355,19 +9349,19 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9387,19 +9381,19 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9419,19 +9413,19 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9451,19 +9445,19 @@
         <v>1</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9483,19 +9477,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9515,25 +9509,25 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>385499.62</v>
+        <v>385499.63</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>15</v>
@@ -9547,19 +9541,19 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9579,19 +9573,19 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9611,19 +9605,19 @@
         <v>15</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D220" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="F220" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9643,19 +9637,19 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9675,25 +9669,25 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>327295.62</v>
+        <v>327295.63</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>15</v>
@@ -9707,19 +9701,19 @@
         <v>4</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9739,19 +9733,19 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9771,19 +9765,19 @@
         <v>4</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9803,19 +9797,19 @@
         <v>4</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9835,19 +9829,19 @@
         <v>4</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9867,19 +9861,19 @@
         <v>4</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9899,19 +9893,19 @@
         <v>3</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9931,19 +9925,19 @@
         <v>1</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9963,19 +9957,19 @@
         <v>4</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9995,19 +9989,19 @@
         <v>1</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -10027,19 +10021,19 @@
         <v>4</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -10059,19 +10053,19 @@
         <v>15</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10091,19 +10085,19 @@
         <v>15</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10123,19 +10117,19 @@
         <v>1</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10155,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10187,19 +10181,19 @@
         <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="F238" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E238" s="2" t="s">
+      <c r="G238" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10219,19 +10213,19 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10251,25 +10245,25 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>494916.62</v>
+        <v>494916.63</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>15</v>
@@ -10283,19 +10277,19 @@
         <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10315,19 +10309,19 @@
         <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10347,19 +10341,19 @@
         <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10379,19 +10373,19 @@
         <v>10</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10411,19 +10405,19 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10443,19 +10437,19 @@
         <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10475,19 +10469,19 @@
         <v>14</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="F247" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10507,19 +10501,19 @@
         <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10539,19 +10533,19 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10571,19 +10565,19 @@
         <v>14</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10603,19 +10597,19 @@
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10635,19 +10629,19 @@
         <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10667,19 +10661,19 @@
         <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10699,19 +10693,19 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10731,19 +10725,19 @@
         <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10763,19 +10757,19 @@
         <v>8</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10795,19 +10789,19 @@
         <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10827,19 +10821,19 @@
         <v>8</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10859,19 +10853,19 @@
         <v>10</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10891,19 +10885,19 @@
         <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10923,19 +10917,19 @@
         <v>8</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10955,19 +10949,19 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10987,19 +10981,19 @@
         <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -11019,19 +11013,19 @@
         <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -11051,19 +11045,19 @@
         <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11083,19 +11077,19 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11115,19 +11109,19 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11147,19 +11141,19 @@
         <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11179,19 +11173,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11211,19 +11205,19 @@
         <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11243,19 +11237,19 @@
         <v>8</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11275,19 +11269,19 @@
         <v>10</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11307,19 +11301,19 @@
         <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11339,19 +11333,19 @@
         <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11371,19 +11365,19 @@
         <v>10</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11403,25 +11397,25 @@
         <v>8</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>307341.12</v>
+        <v>307341.13</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>15</v>
@@ -11435,19 +11429,19 @@
         <v>14</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11467,19 +11461,19 @@
         <v>10</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11499,19 +11493,19 @@
         <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11531,19 +11525,19 @@
         <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11563,19 +11557,19 @@
         <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11595,19 +11589,19 @@
         <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11627,19 +11621,19 @@
         <v>10</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11659,19 +11653,19 @@
         <v>10</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11691,19 +11685,19 @@
         <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11723,19 +11717,19 @@
         <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11755,19 +11749,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11787,19 +11781,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11819,19 +11813,19 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11851,19 +11845,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11883,19 +11877,19 @@
         <v>10</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11915,19 +11909,19 @@
         <v>14</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11947,19 +11941,19 @@
         <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11979,19 +11973,19 @@
         <v>14</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -12011,19 +12005,19 @@
         <v>14</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -12043,25 +12037,25 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>274185.12</v>
+        <v>274185.13</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>15</v>
@@ -12075,19 +12069,19 @@
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12107,19 +12101,19 @@
         <v>9</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12139,19 +12133,19 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12171,19 +12165,19 @@
         <v>14</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12203,19 +12197,19 @@
         <v>8</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12235,25 +12229,25 @@
         <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>264296.62</v>
+        <v>264296.63</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>15</v>
@@ -12267,25 +12261,25 @@
         <v>14</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>263644.12</v>
+        <v>263644.13</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>15</v>
@@ -12299,19 +12293,19 @@
         <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12331,19 +12325,19 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12363,19 +12357,19 @@
         <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12395,19 +12389,19 @@
         <v>8</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12427,19 +12421,19 @@
         <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12459,19 +12453,19 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12491,19 +12485,19 @@
         <v>8</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12523,19 +12517,19 @@
         <v>14</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12555,19 +12549,19 @@
         <v>8</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12587,19 +12581,19 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12619,19 +12613,19 @@
         <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12651,19 +12645,19 @@
         <v>14</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12683,19 +12677,19 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12715,19 +12709,19 @@
         <v>14</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12747,19 +12741,19 @@
         <v>8</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12779,19 +12773,19 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12811,19 +12805,19 @@
         <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12843,19 +12837,19 @@
         <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12875,19 +12869,19 @@
         <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12907,19 +12901,19 @@
         <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12939,19 +12933,19 @@
         <v>9</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12971,19 +12965,19 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -13003,19 +12997,19 @@
         <v>14</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -13035,19 +13029,19 @@
         <v>9</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -13067,19 +13061,19 @@
         <v>10</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13099,19 +13093,19 @@
         <v>9</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13131,19 +13125,19 @@
         <v>9</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13163,19 +13157,19 @@
         <v>10</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13195,19 +13189,19 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13227,19 +13221,19 @@
         <v>8</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>15</v>
@@ -13259,19 +13253,19 @@
         <v>9</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>15</v>
@@ -13291,19 +13285,19 @@
         <v>9</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>15</v>
@@ -13323,19 +13317,19 @@
         <v>9</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>15</v>
@@ -13355,19 +13349,19 @@
         <v>9</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>15</v>
@@ -13387,19 +13381,19 @@
         <v>9</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>15</v>
@@ -13419,19 +13413,19 @@
         <v>9</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>15</v>
@@ -13451,19 +13445,19 @@
         <v>9</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>15</v>
@@ -13483,19 +13477,19 @@
         <v>9</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H341" s="2" t="s">
         <v>15</v>
@@ -13515,19 +13509,19 @@
         <v>9</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H342" s="2" t="s">
         <v>15</v>
@@ -13547,19 +13541,19 @@
         <v>9</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H343" s="2" t="s">
         <v>15</v>
@@ -13579,19 +13573,19 @@
         <v>10</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H344" s="2" t="s">
         <v>15</v>
@@ -13621,7 +13615,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13629,50 +13623,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -13694,21 +13688,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13717,7 +13711,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
